--- a/docs/reports/competitors/2026-08-主要竞争对手自有工厂情况.xlsx
+++ b/docs/reports/competitors/2026-08-主要竞争对手自有工厂情况.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,7 +28,7 @@
     <font>
       <name val="微软雅黑"/>
       <b val="1"/>
-      <color rgb="001E3A5F"/>
+      <color rgb="001F4E79"/>
       <sz val="14"/>
     </font>
     <font>
@@ -46,13 +46,8 @@
       <name val="微软雅黑"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="微软雅黑"/>
-      <color rgb="001E3A5F"/>
-      <sz val="9"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -61,27 +56,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001E3A5F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8F1FB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8F5E9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3E0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFDE7"/>
+        <fgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
   </fills>
@@ -95,56 +70,33 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="008A9BB0"/>
+        <color rgb="00B0B0B0"/>
       </left>
       <right style="thin">
-        <color rgb="008A9BB0"/>
+        <color rgb="00B0B0B0"/>
       </right>
       <top style="thin">
-        <color rgb="008A9BB0"/>
+        <color rgb="00B0B0B0"/>
       </top>
       <bottom style="thin">
-        <color rgb="008A9BB0"/>
+        <color rgb="00B0B0B0"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -511,26 +463,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="68" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>主要竞争对手自有生产制造基地情况一览</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="38" customHeight="1">
+          <t>主要竞争对手自有生产制造基地情况一览（已按官网/权威来源校正）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="40" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>口径：仅统计公司或其全资/控股子公司名下自有工厂/厂区，不含外协代工、合作加工。实荣按内部确认：无自有工厂。资料综合公开信息及内部确认｜仅供内部参考</t>
+          <t>口径：仅统计官网或巨潮资讯等权威披露可支撑的自有工厂/制造基地表述。实荣按内部确认：无自有工厂。详细链接见《2026-08-主要竞争对手自有工厂信息源.xlsx》。核验日期2026-08｜仅供内部参考</t>
         </is>
       </c>
     </row>
@@ -552,15 +504,15 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>自有工厂/基地情况说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="40" customHeight="1">
+          <t>自有工厂/基地情况说明（仅官网/权威）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="42" customHeight="1">
       <c r="A4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>河南实荣筒仓工程有限公司</t>
         </is>
@@ -570,323 +522,323 @@
           <t>否</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>无自有工厂；制造加工依托外协/合作产能，非自有生产基地</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" s="6" t="n">
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>内部确认无自有工厂；官网未见自有工厂面积表述</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1">
+      <c r="A5" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>江苏丰尚智能科技有限公司</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>有自有制造基地，核心为扬州丰尚智慧园等；对外称全球布局约4个生产基地（含在建及海外）</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="40" customHeight="1">
-      <c r="A6" s="6" t="n">
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>官网：4个生产基地；扬州智慧园占地375亩、投资50亿、年产能5万套</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1">
+      <c r="A6" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>江苏丰尚智能仓储装备有限公司</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>否（未见独立自有）</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>未见独立自有大型工厂；钢板仓制造主要依托丰尚集团制造体系</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="40" customHeight="1">
-      <c r="A7" s="6" t="n">
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>未见独立官网自有工厂表述；多依托丰尚集团制造体系</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>中粮科工（中粮工程科技股份有限公司）</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>中粮科工</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>有自有装备制造体系，下属张家口、无锡、南皮、河南装备等制造子公司及工厂；钢板仓制造还依托湖南迎春等下属制造主体</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="40" customHeight="1">
-      <c r="A8" s="6" t="n">
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>官网+年报：张家口/无锡/南皮/河南装备及湖南迎春、山东迎春等制造主体</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1">
+      <c r="A8" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>江苏正昌粮机股份有限公司</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>有自有工厂，位于溧阳正昌产业园区，为集团自有制造基地</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="40" customHeight="1">
-      <c r="A9" s="6" t="n">
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>官网：集团占地400余亩，溧阳正昌路28号</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>江苏国粮仓储工程有限公司</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>否（未见独立自有）</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>偏工程实施主体，制造多依托正昌集团工厂，未见国粮独立大型自有制造基地的清晰公开表述</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="6" t="n">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>是（官网宣称）</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>官网：溧阳生产研发基地近200亩，厂房及办公配套建筑面积8万多㎡，并有多条生产线</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1">
+      <c r="A10" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>安阳利浦筒仓工程有限公司</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>有自有制造能力与生产经营厂区，年产钢板仓约500万立方米</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="6" t="n">
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>官网：装备制造企业，年产钢板仓500万m³；未见官网厂房面积</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>安阳通用国际工矿机械有限公司</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>待谨慎采信</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>仅见AGICO外贸站：30 acres、车间7000㎡；中文官网面积未核清；删6.6万/3万㎡旧数</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1">
+      <c r="A12" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>山东建昌机械有限公司</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>有自有厂区，位于安阳高新区，占地约6.6万平方米、生产车间约3万平方米</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="40" customHeight="1">
-      <c r="A12" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>山东建昌机械有限公司</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>官网有生产现场/厂房设备栏目及平阴孝直镇厂址；未见面积数字</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1">
+      <c r="A13" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>北京双龙 / 安阳宏展</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>本次未见可稳定引用的官网工厂原文</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="42" customHeight="1">
+      <c r="A14" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>河南昊科邦机械设备有限公司</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>有自有生产工厂，专业制造混凝土搅拌站配套水泥仓等产品</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="40" customHeight="1">
-      <c r="A13" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>北京双龙国际工矿机械有限公司 / 安阳市宏展钢板仓工程有限责任公司</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>官网：占地32000㎡，重工业厂房15000㎡</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="42" customHeight="1">
+      <c r="A15" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>山东迎春钢板仓制造有限公司</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>有制造产能，安阳侧存在钢板仓工程与制造主体</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>河南昊科邦机械设备有限公司</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>官网：生产制造钢板仓专业厂家（东营）；未见面积数字</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="42" customHeight="1">
+      <c r="A16" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>辽宁秋然钢板仓有限公司</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>有自有厂房厂区，位于焦作温县</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="40" customHeight="1">
-      <c r="A15" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>山东迎春钢板仓制造有限公司</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>官网：建有7万平方米工业生产基地</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>东营市丰图智能仓储有限公司</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>本次未见可稳定引用的官网工厂原文</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>江苏恒欣仓储设备有限公司</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>有自有生产车间，并下属东营迎春精工等制造主体</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="40" customHeight="1">
-      <c r="A16" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>辽宁秋然钢板仓有限公司</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>有自有生产基地，公开称约7万平方米</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="40" customHeight="1">
-      <c r="A17" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>东营市丰图智能仓储有限公司</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>有厂房（权属待核）</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>有生产厂房并开展制造（注册地址为厂房），公开材料难以确认厂房为自购自建还是租赁</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="40" customHeight="1">
-      <c r="A18" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>江苏恒欣仓储设备有限公司</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>有自有厂区，位于溧阳天目湖前马工业园，建筑面积约2.6万平方米</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="40" customHeight="1">
-      <c r="A19" s="6" t="n">
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>官网：前马工业园，建筑面积26680㎡，办公5000㎡</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>泰安雪莱机械工程有限公司</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>有自有厂区与生产车间，位于泰安北集坡/高新区一带，公开厂房面积约3万平方米量级</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="36" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>小结：多数钢板仓/设备类竞争对手具备自有工厂；实荣无自有工厂，制造依托外协。丰尚仓储装备、国粮更多依托集团工厂；丰图有制造场所，产权是否完全自有尚待核实。</t>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>是（有工厂地址）</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>官网明确工厂地址（北集坡海纳街789号）；未见厂房面积数字</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="48" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>小结：丰尚科技、正昌、国粮（官网宣称）、中粮科工、利浦、昊科邦、迎春、秋然、恒欣、建昌、雪莱（有工厂地址）具备官网可引用的制造/工厂表述；实荣无自有工厂；丰尚仓储装备、双龙/宏展、丰图证据不足；安阳通用仅见AGICO外贸站数字，需谨慎。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A20:D20"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/reports/competitors/2026-08-主要竞争对手自有工厂情况.xlsx
+++ b/docs/reports/competitors/2026-08-主要竞争对手自有工厂情况.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="自有工厂情况" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源链接速查" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,6 +46,12 @@
     <font>
       <name val="微软雅黑"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color rgb="000563C1"/>
+      <sz val="9"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="3">
@@ -86,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -98,6 +105,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -463,30 +476,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>主要竞争对手自有生产制造基地情况一览（已按官网/权威来源校正）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="40" customHeight="1">
+          <t>主要竞争对手自有生产制造基地情况一览（含官网/权威信息源）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>口径：仅统计官网或巨潮资讯等权威披露可支撑的自有工厂/制造基地表述。实荣按内部确认：无自有工厂。详细链接见《2026-08-主要竞争对手自有工厂信息源.xlsx》。核验日期2026-08｜仅供内部参考</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
+          <t>口径：仅统计官网或巨潮资讯等权威披露可支撑的自有工厂/制造基地表述。实荣按内部确认：无自有工厂。核验日期2026-08｜仅供内部参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>序号</t>
@@ -504,11 +519,21 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>自有工厂/基地情况说明（仅官网/权威）</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="42" customHeight="1">
+          <t>自有工厂/基地情况说明</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>信息来源（官网/权威表述）</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>信息来源URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="78" customHeight="1">
       <c r="A4" s="4" t="n">
         <v>1</v>
       </c>
@@ -524,11 +549,21 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>内部确认无自有工厂；官网未见自有工厂面积表述</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="42" customHeight="1">
+          <t>无自有工厂；制造加工依托外协/合作产能，非自有生产基地</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>内部确认：无自有工厂；官网未见自有工厂面积表述</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>—（内部口径）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="78" customHeight="1">
       <c r="A5" s="4" t="n">
         <v>2</v>
       </c>
@@ -544,11 +579,22 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>官网：4个生产基地；扬州智慧园占地375亩、投资50亿、年产能5万套</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="42" customHeight="1">
+          <t>有自有制造基地；官网称全球布局约4个生产基地（含在建）；核心为扬州丰尚智慧园（占地375亩、投资50亿元、年产能5万套）</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>官网：建立了4个生产基地（其中2个在建）；官网新闻：丰尚智慧园总投资50亿元，占地375亩，年产能5万套</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>https://www.famsun.com/about-us
+https://www.famsun.com/resource-news/362.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="78" customHeight="1">
       <c r="A6" s="4" t="n">
         <v>3</v>
       </c>
@@ -564,17 +610,27 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>未见独立官网自有工厂表述；多依托丰尚集团制造体系</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="42" customHeight="1">
+          <t>未见独立自有大型工厂；钢板仓制造主要依托丰尚集团制造体系</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>未见该公司独立官网对自有大型工厂/厂区面积的明确表述</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>—（未见独立官网工厂页）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="78" customHeight="1">
       <c r="A7" s="4" t="n">
         <v>4</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>中粮科工</t>
+          <t>中粮科工（中粮工程科技股份有限公司）</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -584,11 +640,23 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>官网+年报：张家口/无锡/南皮/河南装备及湖南迎春、山东迎春等制造主体</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="42" customHeight="1">
+          <t>有自有装备制造体系；下属张家口、无锡、南皮、河南装备等制造子公司；钢板仓制造还依托湖南迎春等下属制造主体</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>官网：具备装备制造业务板块。巨潮年报：张家口装备、无锡装备、南皮装备、河南装备、湖南迎春、山东迎春等设备制造子公司；披露张家口粮食加工装备制造基地；湖南迎春生产装配式/利浦式/保温钢板仓</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>https://www.cofcoet.com/
+https://static.cninfo.com.cn/finalpage/2025-04-26/1223306758.PDF
+http://static.cninfo.com.cn/finalpage/2022-10-25/1214882253.PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="78" customHeight="1">
       <c r="A8" s="4" t="n">
         <v>5</v>
       </c>
@@ -604,11 +672,21 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>官网：集团占地400余亩，溧阳正昌路28号</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="42" customHeight="1">
+          <t>有自有工厂，位于溧阳正昌产业园区；官网称集团占地400余亩</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>官网：正昌集团占地400余亩；地址江苏省溧阳市正昌路28号</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>https://www.zhengchang.com/about.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="78" customHeight="1">
       <c r="A9" s="4" t="n">
         <v>6</v>
       </c>
@@ -624,11 +702,22 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>官网：溧阳生产研发基地近200亩，厂房及办公配套建筑面积8万多㎡，并有多条生产线</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="42" customHeight="1">
+          <t>官网宣称：2012年溧阳建成现代化生产研发基地，占地近200亩，新建厂房及办公配套设施建筑面积8万多平方米，并有多条生产线</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>官网公司介绍原文：基地占地近200亩，新建厂房及办公配套设施建筑面积8万多平方米；引进多条现代化生产线</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>http://www.guoliang.com/about.html
+http://www.guoliang.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="78" customHeight="1">
       <c r="A10" s="4" t="n">
         <v>7</v>
       </c>
@@ -644,11 +733,22 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>官网：装备制造企业，年产钢板仓500万m³；未见官网厂房面积</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="42" customHeight="1">
+          <t>有自有制造能力与生产经营厂区；官网称年产钢板仓约500万立方米（未见官网给出具体厂房㎡）</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>官网：集科研、设计、生产、安装等配套服务的装备制造企业；员工500多名；年产钢板仓500万立方米制造能力</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>https://www.lipp.com.cn/
+https://www.lipp.com.cn/about.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="78" customHeight="1">
       <c r="A11" s="4" t="n">
         <v>8</v>
       </c>
@@ -664,11 +764,22 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>仅见AGICO外贸站：30 acres、车间7000㎡；中文官网面积未核清；删6.6万/3万㎡旧数</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="42" customHeight="1">
+          <t>关联外贸品牌站AGICO称：安阳高新区，占地30 acres、生产车间7000㎡；中文官网未见同等面积表述。此前“约6.6万㎡/车间约3万㎡”无官网支撑，已剔除</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>仅见AGICO外贸站 about-us 原文（需谨慎，非独立法定披露）</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>https://www.steel-silo.com/about-us.html
+https://www.steel-silo.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="78" customHeight="1">
       <c r="A12" s="4" t="n">
         <v>9</v>
       </c>
@@ -684,17 +795,28 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>官网有生产现场/厂房设备栏目及平阴孝直镇厂址；未见面积数字</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="42" customHeight="1">
+          <t>有自有生产工厂；官网设“生产现场”“厂房设备”栏目，地址平阴县孝直镇盛威路（未见官网面积数字）</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>官网：成立1999年，职工300余人；导航含生产现场/厂房设备；联系地址济南市平阴县孝直镇盛威路</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>http://www.sdjianchang.cn/
+http://www.sdjianchang.cn/contact.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="78" customHeight="1">
       <c r="A13" s="4" t="n">
         <v>10</v>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>北京双龙 / 安阳宏展</t>
+          <t>北京双龙国际工矿机械有限公司 / 安阳市宏展钢板仓工程有限责任公司</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -704,11 +826,21 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>本次未见可稳定引用的官网工厂原文</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="42" customHeight="1">
+          <t>本次未见可稳定引用的官网工厂面积/厂区原文，暂不采信具体工厂数据</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>未见可采信官网原文</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>—（官网暂不可稳定核验）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="78" customHeight="1">
       <c r="A14" s="4" t="n">
         <v>11</v>
       </c>
@@ -724,11 +856,23 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>官网：占地32000㎡，重工业厂房15000㎡</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="42" customHeight="1">
+          <t>有自有厂房厂区；官网称占地32000㎡，标准化重工业厂房15000㎡（温县）</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>官网 Factory 页：covers an area of 32,000 square meters；heavy-duty industrial plant of 15,000 square meters</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hkbsilo.com/factory/
+https://www.hkbsilo.com/
+https://www.hkbsilo.com/contact-us/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="78" customHeight="1">
       <c r="A15" s="4" t="n">
         <v>12</v>
       </c>
@@ -744,11 +888,21 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>官网：生产制造钢板仓专业厂家（东营）；未见面积数字</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="42" customHeight="1">
+          <t>有生产制造能力；官网称生产制造钢板仓专业厂家，位于东营国家级开发区（未见官网厂房面积）</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>官网：是生产制造钢板仓的专业厂家；具有专业研发、设计、生产、安装队伍及配套设备制造能力</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>http://www.gangbancang.cn/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="78" customHeight="1">
       <c r="A16" s="4" t="n">
         <v>13</v>
       </c>
@@ -764,11 +918,21 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>官网：建有7万平方米工业生产基地</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="42" customHeight="1">
+          <t>有自有生产基地；官网称建有7万平方米工业生产基地</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>官网原文：公司建有7万平方米的工业生产基地，拥有现代化厂房和专业化的生产线及检测设备</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>http://www.cnqrgbc.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="78" customHeight="1">
       <c r="A17" s="4" t="n">
         <v>14</v>
       </c>
@@ -784,11 +948,21 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>本次未见可稳定引用的官网工厂原文</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="42" customHeight="1">
+          <t>本次未见可稳定引用的官网自有工厂面积/产权原文，暂不采信具体工厂数据</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>未见可采信官网原文</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>—（官网暂不可稳定核验）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="78" customHeight="1">
       <c r="A18" s="4" t="n">
         <v>15</v>
       </c>
@@ -804,11 +978,21 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>官网：前马工业园，建筑面积26680㎡，办公5000㎡</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="42" customHeight="1">
+          <t>有自有厂区；官网称位于溧阳天目湖前马工业园，建筑面积26680㎡，办公面积5000㎡</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>官网原文：坐落天目湖畔前马工业园区，公司建筑面积26680平方米，办公面积5000平方米，生产型企业</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hengxinsilo.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="78" customHeight="1">
       <c r="A19" s="4" t="n">
         <v>16</v>
       </c>
@@ -824,23 +1008,355 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>官网明确工厂地址（北集坡海纳街789号）；未见厂房面积数字</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="48" customHeight="1">
+          <t>官网明确工厂地址：泰安市岱岳区北集坡街道海纳街789号；未见官网厂房面积数字（此前“约3万㎡”已剔除）</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>官网页脚：工厂地址＝山东省泰安市岱岳区北集坡街道海纳街789号；集研发、设计、制造、销售及维修于一体</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>http://www.cnshelley.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="52" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>小结：丰尚科技、正昌、国粮（官网宣称）、中粮科工、利浦、昊科邦、迎春、秋然、恒欣、建昌、雪莱（有工厂地址）具备官网可引用的制造/工厂表述；实荣无自有工厂；丰尚仓储装备、双龙/宏展、丰图证据不足；安阳通用仅见AGICO外贸站数字，需谨慎。</t>
+          <t>小结：丰尚科技、正昌、国粮（官网宣称）、中粮科工、利浦、昊科邦、迎春、秋然、恒欣、建昌、雪莱（有工厂地址）具备官网可引用的制造/工厂表述；实荣无自有工厂；丰尚仓储装备、双龙/宏展、丰图证据不足；安阳通用仅见AGICO外贸站数字，需谨慎。信息源仅限企业官网或巨潮资讯等权威披露。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId12"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="78" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>公司</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>链接</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>丰尚智能科技</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>https://www.famsun.com/about-us</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>官网</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>丰尚智慧园新闻</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>https://www.famsun.com/resource-news/362.html</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>官网新闻</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>正昌粮机</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>https://www.zhengchang.com/about.html</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>官网</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>国粮仓储</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>http://www.guoliang.com/about.html</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>官网</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>中粮科工</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>https://www.cofcoet.com/</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>官网</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>中粮科工2024年报（巨潮）</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>https://static.cninfo.com.cn/finalpage/2025-04-26/1223306758.PDF</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>巨潮资讯</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>中粮科工2022三季报</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>http://static.cninfo.com.cn/finalpage/2022-10-25/1214882253.PDF</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>巨潮资讯</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>安阳利浦</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>https://www.lipp.com.cn/about.html</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>官网</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>昊科邦Factory</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>https://www.hkbsilo.com/factory/</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>官网</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>秋然钢板仓</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>http://www.cnqrgbc.com/</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>官网</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>恒欣仓储</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>https://www.hengxinsilo.com/</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>官网</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>雪莱</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>http://www.cnshelley.com/</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>官网</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>山东迎春</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>http://www.gangbancang.cn/</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>官网</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>山东建昌</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>http://www.sdjianchang.cn/</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>官网</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>AGICO外贸站（谨慎）</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>https://www.steel-silo.com/about-us.html</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>关联品牌站</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>